--- a/public/exports-60-250/29188572.xlsx
+++ b/public/exports-60-250/29188572.xlsx
@@ -7489,12 +7489,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042252</t>
+          <t xml:space="preserve">200042241</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042252</t>
+          <t xml:space="preserve">200042241</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056746</t>
+          <t xml:space="preserve">200056744</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
